--- a/Use_Cases/Cost Comparison Tool/Datasets/cleaned_ev_vehicles.xlsx
+++ b/Use_Cases/Cost Comparison Tool/Datasets/cleaned_ev_vehicles.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e0c7967e7d16fc8/Documents/GitHub/EVAT-Data-Science/Use_Cases/Cost Comparison Tool/Datasets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="389" documentId="11_FFC65FC0CDD1E8D68A160B00A3B349A577805E32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7877FD85-3938-4126-B518-AD066F10D509}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="222">
   <si>
     <t>_id</t>
   </si>
@@ -584,13 +590,109 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>EV3</t>
+  </si>
+  <si>
+    <t>iX3</t>
+  </si>
+  <si>
+    <t>Hyundai</t>
+  </si>
+  <si>
+    <t>Ioniq 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesla </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kia </t>
+  </si>
+  <si>
+    <t>EV5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leapmotor </t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>EX30</t>
+  </si>
+  <si>
+    <t>Toyota</t>
+  </si>
+  <si>
+    <t>bZ4X</t>
+  </si>
+  <si>
+    <t>Xpeng</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeekr </t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Polestar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Y </t>
+  </si>
+  <si>
+    <t>50 xDrive AWD</t>
+  </si>
+  <si>
+    <t>BEV</t>
+  </si>
+  <si>
+    <t>Single Motor RWD</t>
+  </si>
+  <si>
+    <t>FWD</t>
+  </si>
+  <si>
+    <t>RWD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air SR </t>
+  </si>
+  <si>
+    <t>Calligraphy</t>
+  </si>
+  <si>
+    <t>Standard Range 2WD</t>
+  </si>
+  <si>
+    <t>Standard 18 inch</t>
+  </si>
+  <si>
+    <t>200kW Long Range Single Motor</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>RWD H6MRB</t>
+  </si>
+  <si>
+    <t>RWD YS6MRB</t>
+  </si>
+  <si>
+    <t>AWD Long Range YL5NDB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,10 +744,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -653,13 +758,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -697,7 +810,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -731,6 +844,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -765,9 +879,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -940,11 +1055,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X73"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="17.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" customWidth="1"/>
+    <col min="16" max="16" width="28.42578125" customWidth="1"/>
+    <col min="17" max="17" width="26.85546875" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" customWidth="1"/>
+    <col min="19" max="19" width="22.28515625" customWidth="1"/>
+    <col min="20" max="20" width="17.140625" customWidth="1"/>
+    <col min="21" max="21" width="17" customWidth="1"/>
+    <col min="22" max="22" width="18.42578125" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" customWidth="1"/>
+    <col min="24" max="24" width="16.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +1159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1092,7 +1233,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1166,7 +1307,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1240,7 +1381,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1314,7 +1455,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1388,7 +1529,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1462,7 +1603,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1536,7 +1677,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1610,7 +1751,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1684,7 +1825,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -1758,7 +1899,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -1832,7 +1973,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1906,7 +2047,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1980,7 +2121,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -2054,7 +2195,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2128,7 +2269,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2202,7 +2343,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -2276,7 +2417,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2350,7 +2491,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -2424,7 +2565,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2498,7 +2639,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -2572,7 +2713,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -2646,7 +2787,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -2720,7 +2861,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -2794,7 +2935,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -2868,7 +3009,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -2942,7 +3083,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -3016,7 +3157,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -3090,7 +3231,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -3164,7 +3305,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -3238,7 +3379,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>54</v>
       </c>
@@ -3312,7 +3453,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -3386,7 +3527,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>56</v>
       </c>
@@ -3460,7 +3601,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -3534,7 +3675,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -3608,7 +3749,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -3682,7 +3823,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>60</v>
       </c>
@@ -3756,7 +3897,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>61</v>
       </c>
@@ -3830,7 +3971,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -3904,7 +4045,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>63</v>
       </c>
@@ -3978,7 +4119,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>64</v>
       </c>
@@ -4052,7 +4193,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>65</v>
       </c>
@@ -4126,7 +4267,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -4200,7 +4341,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -4274,7 +4415,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>68</v>
       </c>
@@ -4348,7 +4489,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>69</v>
       </c>
@@ -4422,7 +4563,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -4496,7 +4637,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>71</v>
       </c>
@@ -4570,7 +4711,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>72</v>
       </c>
@@ -4644,7 +4785,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>73</v>
       </c>
@@ -4718,7 +4859,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>74</v>
       </c>
@@ -4792,7 +4933,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>75</v>
       </c>
@@ -4866,7 +5007,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>76</v>
       </c>
@@ -4940,7 +5081,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>77</v>
       </c>
@@ -5014,7 +5155,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>78</v>
       </c>
@@ -5088,7 +5229,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>79</v>
       </c>
@@ -5162,7 +5303,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>80</v>
       </c>
@@ -5236,7 +5377,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -5310,7 +5451,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -5382,6 +5523,929 @@
       </c>
       <c r="X60">
         <v>1075</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>2026</v>
+      </c>
+      <c r="C61" t="s">
+        <v>90</v>
+      </c>
+      <c r="D61" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" t="s">
+        <v>208</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="s">
+        <v>178</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61" t="s">
+        <v>179</v>
+      </c>
+      <c r="J61">
+        <v>4</v>
+      </c>
+      <c r="K61">
+        <v>5</v>
+      </c>
+      <c r="L61" t="s">
+        <v>183</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61" t="s">
+        <v>186</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>188</v>
+      </c>
+      <c r="R61">
+        <v>634</v>
+      </c>
+      <c r="S61" t="s">
+        <v>187</v>
+      </c>
+      <c r="T61" t="s">
+        <v>188</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>130</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>2025</v>
+      </c>
+      <c r="C62" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" t="s">
+        <v>190</v>
+      </c>
+      <c r="E62" t="s">
+        <v>213</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="s">
+        <v>178</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62" t="s">
+        <v>179</v>
+      </c>
+      <c r="J62">
+        <v>4</v>
+      </c>
+      <c r="K62">
+        <v>5</v>
+      </c>
+      <c r="L62" t="s">
+        <v>184</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62" t="s">
+        <v>186</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>149</v>
+      </c>
+      <c r="R62">
+        <v>436</v>
+      </c>
+      <c r="S62" t="s">
+        <v>187</v>
+      </c>
+      <c r="T62" t="s">
+        <v>188</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>103</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>2025</v>
+      </c>
+      <c r="C63" t="s">
+        <v>192</v>
+      </c>
+      <c r="D63" t="s">
+        <v>193</v>
+      </c>
+      <c r="E63" t="s">
+        <v>214</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" t="s">
+        <v>178</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63" t="s">
+        <v>179</v>
+      </c>
+      <c r="J63">
+        <v>4</v>
+      </c>
+      <c r="K63">
+        <v>6</v>
+      </c>
+      <c r="L63" t="s">
+        <v>184</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63" t="s">
+        <v>186</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>206</v>
+      </c>
+      <c r="R63">
+        <v>600</v>
+      </c>
+      <c r="S63" t="s">
+        <v>187</v>
+      </c>
+      <c r="T63" t="s">
+        <v>188</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>142</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>2024</v>
+      </c>
+      <c r="C64" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" t="s">
+        <v>101</v>
+      </c>
+      <c r="E64" t="s">
+        <v>219</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>178</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64" t="s">
+        <v>179</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="L64" t="s">
+        <v>182</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
+      </c>
+      <c r="N64" t="s">
+        <v>186</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>138</v>
+      </c>
+      <c r="R64">
+        <v>520</v>
+      </c>
+      <c r="S64" t="s">
+        <v>187</v>
+      </c>
+      <c r="T64" t="s">
+        <v>188</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>95</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B65">
+        <v>2025</v>
+      </c>
+      <c r="C65" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" t="s">
+        <v>220</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="s">
+        <v>178</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65">
+        <v>4</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65" t="s">
+        <v>184</v>
+      </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
+      <c r="N65" t="s">
+        <v>186</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>153</v>
+      </c>
+      <c r="R65">
+        <v>466</v>
+      </c>
+      <c r="S65" t="s">
+        <v>187</v>
+      </c>
+      <c r="T65" t="s">
+        <v>188</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>106</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B66">
+        <v>2026</v>
+      </c>
+      <c r="C66" t="s">
+        <v>194</v>
+      </c>
+      <c r="D66" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" t="s">
+        <v>221</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>178</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66" t="s">
+        <v>179</v>
+      </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+      <c r="K66">
+        <v>6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>184</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66" t="s">
+        <v>186</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>146</v>
+      </c>
+      <c r="R66">
+        <v>681</v>
+      </c>
+      <c r="S66" t="s">
+        <v>187</v>
+      </c>
+      <c r="T66" t="s">
+        <v>188</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>101</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B67">
+        <v>2024</v>
+      </c>
+      <c r="C67" t="s">
+        <v>195</v>
+      </c>
+      <c r="D67" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" t="s">
+        <v>215</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67" t="s">
+        <v>178</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67" t="s">
+        <v>179</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+      <c r="L67" t="s">
+        <v>184</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67" t="s">
+        <v>186</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>182</v>
+      </c>
+      <c r="R67">
+        <v>400</v>
+      </c>
+      <c r="S67" t="s">
+        <v>187</v>
+      </c>
+      <c r="T67" t="s">
+        <v>188</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>126</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B68">
+        <v>2025</v>
+      </c>
+      <c r="C68" t="s">
+        <v>197</v>
+      </c>
+      <c r="D68" t="s">
+        <v>198</v>
+      </c>
+      <c r="E68" t="s">
+        <v>209</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" t="s">
+        <v>178</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>179</v>
+      </c>
+      <c r="J68">
+        <v>4</v>
+      </c>
+      <c r="K68">
+        <v>5</v>
+      </c>
+      <c r="L68" t="s">
+        <v>184</v>
+      </c>
+      <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68" t="s">
+        <v>186</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>163</v>
+      </c>
+      <c r="R68">
+        <v>480</v>
+      </c>
+      <c r="S68" t="s">
+        <v>187</v>
+      </c>
+      <c r="T68" t="s">
+        <v>188</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>112</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B69">
+        <v>2024</v>
+      </c>
+      <c r="C69" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" t="s">
+        <v>199</v>
+      </c>
+      <c r="E69" t="s">
+        <v>210</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69" t="s">
+        <v>178</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69" t="s">
+        <v>179</v>
+      </c>
+      <c r="J69">
+        <v>4</v>
+      </c>
+      <c r="K69">
+        <v>5</v>
+      </c>
+      <c r="L69" t="s">
+        <v>181</v>
+      </c>
+      <c r="M69">
+        <v>2</v>
+      </c>
+      <c r="N69" t="s">
+        <v>186</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>175</v>
+      </c>
+      <c r="R69">
+        <v>462</v>
+      </c>
+      <c r="S69" t="s">
+        <v>187</v>
+      </c>
+      <c r="T69" t="s">
+        <v>188</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>121</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+      <c r="X69">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70">
+        <v>2025</v>
+      </c>
+      <c r="C70" t="s">
+        <v>200</v>
+      </c>
+      <c r="D70" t="s">
+        <v>201</v>
+      </c>
+      <c r="E70" t="s">
+        <v>211</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>178</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>179</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70">
+        <v>5</v>
+      </c>
+      <c r="L70" t="s">
+        <v>183</v>
+      </c>
+      <c r="M70">
+        <v>2</v>
+      </c>
+      <c r="N70" t="s">
+        <v>186</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>138</v>
+      </c>
+      <c r="R70">
+        <v>591</v>
+      </c>
+      <c r="S70" t="s">
+        <v>187</v>
+      </c>
+      <c r="T70" t="s">
+        <v>188</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>95</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71">
+        <v>2024</v>
+      </c>
+      <c r="C71" t="s">
+        <v>202</v>
+      </c>
+      <c r="D71" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" t="s">
+        <v>216</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>178</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71" t="s">
+        <v>179</v>
+      </c>
+      <c r="J71">
+        <v>4</v>
+      </c>
+      <c r="K71">
+        <v>5</v>
+      </c>
+      <c r="L71" t="s">
+        <v>182</v>
+      </c>
+      <c r="M71">
+        <v>2</v>
+      </c>
+      <c r="N71" t="s">
+        <v>186</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>159</v>
+      </c>
+      <c r="R71">
+        <v>525</v>
+      </c>
+      <c r="S71" t="s">
+        <v>187</v>
+      </c>
+      <c r="T71" t="s">
+        <v>188</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>110</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72">
+        <v>2024</v>
+      </c>
+      <c r="C72" t="s">
+        <v>204</v>
+      </c>
+      <c r="D72" t="s">
+        <v>205</v>
+      </c>
+      <c r="E72" t="s">
+        <v>212</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>178</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72" t="s">
+        <v>218</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <v>5</v>
+      </c>
+      <c r="L72" t="s">
+        <v>184</v>
+      </c>
+      <c r="M72">
+        <v>2</v>
+      </c>
+      <c r="N72" t="s">
+        <v>186</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>139</v>
+      </c>
+      <c r="R72">
+        <v>540</v>
+      </c>
+      <c r="S72" t="s">
+        <v>187</v>
+      </c>
+      <c r="T72" t="s">
+        <v>188</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>96</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B73">
+        <v>2025</v>
+      </c>
+      <c r="C73" t="s">
+        <v>206</v>
+      </c>
+      <c r="D73" s="2">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
+        <v>217</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" t="s">
+        <v>178</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73" t="s">
+        <v>179</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73">
+        <v>5</v>
+      </c>
+      <c r="L73" t="s">
+        <v>184</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73" t="s">
+        <v>186</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>184</v>
+      </c>
+      <c r="R73">
+        <v>620</v>
+      </c>
+      <c r="S73" t="s">
+        <v>187</v>
+      </c>
+      <c r="T73" t="s">
+        <v>188</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>127</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>927</v>
       </c>
     </row>
   </sheetData>
